--- a/Plant_Height_data.xlsx
+++ b/Plant_Height_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajen\OneDrive\Desktop\Arranged_Dataset\Draft Manual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmishra\OneDrive - Kansas State University\Desktop\Draft Manual\Li_6800 Manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78D6DE49-CB67-4D5C-847F-98FBB5F3B3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F90EDE-3442-4B72-924D-9E6FAFEF1F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">Plot Number </t>
   </si>
@@ -46,6 +46,18 @@
   </si>
   <si>
     <t xml:space="preserve">Date of Measuremnt </t>
+  </si>
+  <si>
+    <t>23-08-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yield and Yield parameter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of rows </t>
+  </si>
+  <si>
+    <t xml:space="preserve">per row number </t>
   </si>
 </sst>
 </file>
@@ -90,7 +102,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -135,11 +147,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -165,6 +190,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,17 +474,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O171"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" style="15" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="10" max="10" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -478,8 +508,17 @@
       <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -499,8 +538,11 @@
       <c r="G2" s="12">
         <v>46257</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H2" s="14"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -517,8 +559,12 @@
       <c r="F3" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G3" s="8"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -535,8 +581,12 @@
       <c r="F4" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G4" s="8"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>1</v>
       </c>
@@ -553,8 +603,12 @@
       <c r="F5" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G5" s="8"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>1</v>
       </c>
@@ -571,10 +625,14 @@
       <c r="F6" s="11">
         <v>1</v>
       </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>1</v>
       </c>
@@ -591,10 +649,14 @@
       <c r="F7" s="11">
         <v>1</v>
       </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
       <c r="N7" s="2"/>
       <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1</v>
       </c>
@@ -613,10 +675,14 @@
       <c r="F8" s="11">
         <v>1</v>
       </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
       <c r="N8" s="2"/>
       <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>1</v>
       </c>
@@ -635,10 +701,14 @@
       <c r="F9" s="11">
         <v>1</v>
       </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
       <c r="N9" s="2"/>
       <c r="O9" s="3"/>
     </row>
-    <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>2</v>
       </c>
@@ -655,10 +725,14 @@
       <c r="F10" s="11">
         <v>0</v>
       </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
       <c r="N10" s="2"/>
       <c r="O10" s="3"/>
     </row>
-    <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>2</v>
       </c>
@@ -675,10 +749,14 @@
       <c r="F11" s="11">
         <v>1</v>
       </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
       <c r="N11" s="2"/>
       <c r="O11" s="3"/>
     </row>
-    <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>2</v>
       </c>
@@ -695,10 +773,14 @@
       <c r="F12" s="11">
         <v>1</v>
       </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
       <c r="N12" s="2"/>
       <c r="O12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>2</v>
       </c>
@@ -715,10 +797,14 @@
       <c r="F13" s="11">
         <v>1</v>
       </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
       <c r="N13" s="2"/>
       <c r="O13" s="3"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>2</v>
       </c>
@@ -735,10 +821,14 @@
       <c r="F14" s="11">
         <v>0</v>
       </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
       <c r="N14" s="4"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>2</v>
       </c>
@@ -755,8 +845,12 @@
       <c r="F15" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G15" s="8"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>2</v>
       </c>
@@ -773,8 +867,12 @@
       <c r="F16" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="8"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>3</v>
       </c>
@@ -791,8 +889,12 @@
       <c r="F17" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="8"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>3</v>
       </c>
@@ -809,8 +911,12 @@
       <c r="F18" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="8"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>3</v>
       </c>
@@ -827,8 +933,12 @@
       <c r="F19" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="8"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>3</v>
       </c>
@@ -845,8 +955,12 @@
       <c r="F20" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="8"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>3</v>
       </c>
@@ -863,8 +977,12 @@
       <c r="F21" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="8"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>3</v>
       </c>
@@ -881,8 +999,12 @@
       <c r="F22" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="8"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>4</v>
       </c>
@@ -899,8 +1021,12 @@
       <c r="F23" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="8"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>4</v>
       </c>
@@ -917,8 +1043,12 @@
       <c r="F24" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="8"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>4</v>
       </c>
@@ -935,8 +1065,12 @@
       <c r="F25" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="8"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>4</v>
       </c>
@@ -953,8 +1087,12 @@
       <c r="F26" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="8"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>4</v>
       </c>
@@ -971,8 +1109,12 @@
       <c r="F27" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="8"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>4</v>
       </c>
@@ -989,8 +1131,12 @@
       <c r="F28" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="8"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>5</v>
       </c>
@@ -1007,8 +1153,12 @@
       <c r="F29" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="8"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>5</v>
       </c>
@@ -1025,8 +1175,12 @@
       <c r="F30" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="8"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>5</v>
       </c>
@@ -1043,8 +1197,12 @@
       <c r="F31" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="8"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>5</v>
       </c>
@@ -1061,8 +1219,12 @@
       <c r="F32" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="8"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>5</v>
       </c>
@@ -1079,8 +1241,12 @@
       <c r="F33" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="8"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>5</v>
       </c>
@@ -1097,8 +1263,12 @@
       <c r="F34" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="8"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>6</v>
       </c>
@@ -1115,8 +1285,12 @@
       <c r="F35" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="8"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>6</v>
       </c>
@@ -1133,8 +1307,12 @@
       <c r="F36" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36" s="8"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>6</v>
       </c>
@@ -1151,8 +1329,12 @@
       <c r="F37" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="8"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>6</v>
       </c>
@@ -1169,8 +1351,12 @@
       <c r="F38" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="8"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>6</v>
       </c>
@@ -1189,8 +1375,12 @@
       <c r="F39" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39" s="8"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>6</v>
       </c>
@@ -1207,8 +1397,12 @@
       <c r="F40" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40" s="8"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>7</v>
       </c>
@@ -1225,8 +1419,12 @@
       <c r="F41" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="8"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>7</v>
       </c>
@@ -1243,8 +1441,12 @@
       <c r="F42" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42" s="8"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>7</v>
       </c>
@@ -1261,8 +1463,12 @@
       <c r="F43" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43" s="8"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>7</v>
       </c>
@@ -1279,8 +1485,12 @@
       <c r="F44" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44" s="8"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>7</v>
       </c>
@@ -1297,8 +1507,12 @@
       <c r="F45" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45" s="8"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>7</v>
       </c>
@@ -1315,8 +1529,12 @@
       <c r="F46" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46" s="8"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>8</v>
       </c>
@@ -1335,8 +1553,18 @@
       <c r="F47" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="14"/>
+      <c r="I47" s="8">
+        <v>29</v>
+      </c>
+      <c r="J47" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>8</v>
       </c>
@@ -1353,8 +1581,12 @@
       <c r="F48" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48" s="8"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <v>8</v>
       </c>
@@ -1371,8 +1603,12 @@
       <c r="F49" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G49" s="8"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <v>8</v>
       </c>
@@ -1389,8 +1625,12 @@
       <c r="F50" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G50" s="8"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>8</v>
       </c>
@@ -1407,8 +1647,12 @@
       <c r="F51" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G51" s="8"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>8</v>
       </c>
@@ -1425,8 +1669,12 @@
       <c r="F52" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G52" s="8"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>8</v>
       </c>
@@ -1443,8 +1691,12 @@
       <c r="F53" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G53" s="8"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>9</v>
       </c>
@@ -1461,8 +1713,12 @@
       <c r="F54" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G54" s="8"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>9</v>
       </c>
@@ -1479,8 +1735,12 @@
       <c r="F55" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G55" s="8"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <v>9</v>
       </c>
@@ -1497,8 +1757,12 @@
       <c r="F56" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G56" s="8"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>9</v>
       </c>
@@ -1515,8 +1779,12 @@
       <c r="F57" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G57" s="8"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <v>9</v>
       </c>
@@ -1533,8 +1801,12 @@
       <c r="F58" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G58" s="8"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>9</v>
       </c>
@@ -1551,8 +1823,12 @@
       <c r="F59" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G59" s="8"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>10</v>
       </c>
@@ -1569,8 +1845,12 @@
       <c r="F60" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G60" s="8"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>10</v>
       </c>
@@ -1587,8 +1867,12 @@
       <c r="F61" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G61" s="8"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <v>10</v>
       </c>
@@ -1605,8 +1889,12 @@
       <c r="F62" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G62" s="8"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>10</v>
       </c>
@@ -1623,8 +1911,12 @@
       <c r="F63" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G63" s="8"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <v>10</v>
       </c>
@@ -1641,8 +1933,12 @@
       <c r="F64" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G64" s="8"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="8"/>
+      <c r="J64" s="8"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <v>10</v>
       </c>
@@ -1659,8 +1955,12 @@
       <c r="F65" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G65" s="8"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>10</v>
       </c>
@@ -1679,8 +1979,12 @@
       <c r="F66" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G66" s="8"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <v>11</v>
       </c>
@@ -1697,8 +2001,12 @@
       <c r="F67" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G67" s="8"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>11</v>
       </c>
@@ -1715,8 +2023,12 @@
       <c r="F68" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G68" s="8"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>11</v>
       </c>
@@ -1733,8 +2045,12 @@
       <c r="F69" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G69" s="8"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>11</v>
       </c>
@@ -1751,8 +2067,12 @@
       <c r="F70" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G70" s="8"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>11</v>
       </c>
@@ -1769,8 +2089,12 @@
       <c r="F71" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G71" s="8"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>11</v>
       </c>
@@ -1787,8 +2111,12 @@
       <c r="F72" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G72" s="8"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>12</v>
       </c>
@@ -1805,8 +2133,12 @@
       <c r="F73" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G73" s="8"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>12</v>
       </c>
@@ -1823,8 +2155,12 @@
       <c r="F74" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G74" s="8"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>12</v>
       </c>
@@ -1841,8 +2177,12 @@
       <c r="F75" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G75" s="8"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>12</v>
       </c>
@@ -1859,8 +2199,12 @@
       <c r="F76" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G76" s="8"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>12</v>
       </c>
@@ -1877,8 +2221,12 @@
       <c r="F77" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G77" s="8"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <v>12</v>
       </c>
@@ -1895,8 +2243,12 @@
       <c r="F78" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G78" s="8"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>13</v>
       </c>
@@ -1913,8 +2265,12 @@
       <c r="F79" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G79" s="8"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <v>13</v>
       </c>
@@ -1931,8 +2287,12 @@
       <c r="F80" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G80" s="8"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <v>13</v>
       </c>
@@ -1949,8 +2309,12 @@
       <c r="F81" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G81" s="8"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
         <v>13</v>
       </c>
@@ -1967,8 +2331,12 @@
       <c r="F82" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G82" s="8"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <v>13</v>
       </c>
@@ -1985,8 +2353,12 @@
       <c r="F83" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G83" s="8"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>13</v>
       </c>
@@ -2003,8 +2375,12 @@
       <c r="F84" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G84" s="8"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>14</v>
       </c>
@@ -2021,8 +2397,12 @@
       <c r="F85" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G85" s="8"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>14</v>
       </c>
@@ -2039,8 +2419,12 @@
       <c r="F86" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G86" s="8"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>14</v>
       </c>
@@ -2057,8 +2441,12 @@
       <c r="F87" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G87" s="8"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <v>14</v>
       </c>
@@ -2075,8 +2463,12 @@
       <c r="F88" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G88" s="8"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="8"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>14</v>
       </c>
@@ -2093,8 +2485,12 @@
       <c r="F89" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G89" s="8"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="8"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <v>14</v>
       </c>
@@ -2111,8 +2507,12 @@
       <c r="F90" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G90" s="8"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="8"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>15</v>
       </c>
@@ -2129,8 +2529,12 @@
       <c r="F91" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G91" s="8"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="8"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
         <v>15</v>
       </c>
@@ -2149,8 +2553,12 @@
       <c r="F92" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G92" s="8"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
         <v>15</v>
       </c>
@@ -2167,8 +2575,12 @@
       <c r="F93" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G93" s="8"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
         <v>15</v>
       </c>
@@ -2185,8 +2597,12 @@
       <c r="F94" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G94" s="8"/>
+      <c r="H94" s="14"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
         <v>15</v>
       </c>
@@ -2203,8 +2619,12 @@
       <c r="F95" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G95" s="8"/>
+      <c r="H95" s="14"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="8">
         <v>15</v>
       </c>
@@ -2221,8 +2641,12 @@
       <c r="F96" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G96" s="8"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
         <v>16</v>
       </c>
@@ -2239,8 +2663,12 @@
       <c r="F97" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G97" s="8"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="8">
         <v>16</v>
       </c>
@@ -2257,8 +2685,12 @@
       <c r="F98" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G98" s="8"/>
+      <c r="H98" s="14"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="8"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
         <v>16</v>
       </c>
@@ -2275,8 +2707,12 @@
       <c r="F99" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G99" s="8"/>
+      <c r="H99" s="14"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="8">
         <v>16</v>
       </c>
@@ -2293,8 +2729,12 @@
       <c r="F100" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G100" s="8"/>
+      <c r="H100" s="14"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
         <v>16</v>
       </c>
@@ -2313,8 +2753,12 @@
       <c r="F101" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G101" s="8"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
         <v>16</v>
       </c>
@@ -2331,8 +2775,12 @@
       <c r="F102" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G102" s="8"/>
+      <c r="H102" s="14"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
         <v>17</v>
       </c>
@@ -2351,8 +2799,12 @@
       <c r="F103" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G103" s="8"/>
+      <c r="H103" s="14"/>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="8">
         <v>17</v>
       </c>
@@ -2369,8 +2821,12 @@
       <c r="F104" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G104" s="8"/>
+      <c r="H104" s="14"/>
+      <c r="I104" s="8"/>
+      <c r="J104" s="8"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
         <v>17</v>
       </c>
@@ -2387,8 +2843,12 @@
       <c r="F105" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G105" s="8"/>
+      <c r="H105" s="14"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="8">
         <v>17</v>
       </c>
@@ -2405,8 +2865,12 @@
       <c r="F106" s="11">
         <v>2</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G106" s="8"/>
+      <c r="H106" s="14"/>
+      <c r="I106" s="8"/>
+      <c r="J106" s="8"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
         <v>17</v>
       </c>
@@ -2423,8 +2887,12 @@
       <c r="F107" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G107" s="8"/>
+      <c r="H107" s="14"/>
+      <c r="I107" s="8"/>
+      <c r="J107" s="8"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="8">
         <v>17</v>
       </c>
@@ -2441,8 +2909,12 @@
       <c r="F108" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G108" s="8"/>
+      <c r="H108" s="14"/>
+      <c r="I108" s="8"/>
+      <c r="J108" s="8"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
         <v>18</v>
       </c>
@@ -2459,8 +2931,12 @@
       <c r="F109" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G109" s="8"/>
+      <c r="H109" s="14"/>
+      <c r="I109" s="8"/>
+      <c r="J109" s="8"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="8">
         <v>18</v>
       </c>
@@ -2477,8 +2953,12 @@
       <c r="F110" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G110" s="8"/>
+      <c r="H110" s="14"/>
+      <c r="I110" s="8"/>
+      <c r="J110" s="8"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
         <v>18</v>
       </c>
@@ -2495,8 +2975,12 @@
       <c r="F111" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G111" s="8"/>
+      <c r="H111" s="14"/>
+      <c r="I111" s="8"/>
+      <c r="J111" s="8"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="8">
         <v>18</v>
       </c>
@@ -2513,8 +2997,12 @@
       <c r="F112" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G112" s="8"/>
+      <c r="H112" s="14"/>
+      <c r="I112" s="8"/>
+      <c r="J112" s="8"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
         <v>18</v>
       </c>
@@ -2531,8 +3019,12 @@
       <c r="F113" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G113" s="8"/>
+      <c r="H113" s="14"/>
+      <c r="I113" s="8"/>
+      <c r="J113" s="8"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="8">
         <v>18</v>
       </c>
@@ -2549,8 +3041,12 @@
       <c r="F114" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G114" s="8"/>
+      <c r="H114" s="14"/>
+      <c r="I114" s="8"/>
+      <c r="J114" s="8"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
         <v>19</v>
       </c>
@@ -2569,8 +3065,12 @@
       <c r="F115" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G115" s="8"/>
+      <c r="H115" s="14"/>
+      <c r="I115" s="8"/>
+      <c r="J115" s="8"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="8">
         <v>19</v>
       </c>
@@ -2587,8 +3087,12 @@
       <c r="F116" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G116" s="8"/>
+      <c r="H116" s="14"/>
+      <c r="I116" s="8"/>
+      <c r="J116" s="8"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="8">
         <v>19</v>
       </c>
@@ -2605,8 +3109,12 @@
       <c r="F117" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G117" s="8"/>
+      <c r="H117" s="14"/>
+      <c r="I117" s="8"/>
+      <c r="J117" s="8"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
         <v>19</v>
       </c>
@@ -2623,8 +3131,12 @@
       <c r="F118" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G118" s="8"/>
+      <c r="H118" s="14"/>
+      <c r="I118" s="8"/>
+      <c r="J118" s="8"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="8">
         <v>19</v>
       </c>
@@ -2641,8 +3153,12 @@
       <c r="F119" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G119" s="8"/>
+      <c r="H119" s="14"/>
+      <c r="I119" s="8"/>
+      <c r="J119" s="8"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
         <v>19</v>
       </c>
@@ -2659,8 +3175,12 @@
       <c r="F120" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G120" s="8"/>
+      <c r="H120" s="14"/>
+      <c r="I120" s="8"/>
+      <c r="J120" s="8"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="8">
         <v>19</v>
       </c>
@@ -2677,8 +3197,12 @@
       <c r="F121" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G121" s="8"/>
+      <c r="H121" s="14"/>
+      <c r="I121" s="8"/>
+      <c r="J121" s="8"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
         <v>20</v>
       </c>
@@ -2695,8 +3219,12 @@
       <c r="F122" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G122" s="8"/>
+      <c r="H122" s="14"/>
+      <c r="I122" s="8"/>
+      <c r="J122" s="8"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="8">
         <v>20</v>
       </c>
@@ -2713,8 +3241,12 @@
       <c r="F123" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G123" s="8"/>
+      <c r="H123" s="14"/>
+      <c r="I123" s="8"/>
+      <c r="J123" s="8"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
         <v>20</v>
       </c>
@@ -2731,8 +3263,12 @@
       <c r="F124" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G124" s="8"/>
+      <c r="H124" s="14"/>
+      <c r="I124" s="8"/>
+      <c r="J124" s="8"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="8">
         <v>20</v>
       </c>
@@ -2749,8 +3285,12 @@
       <c r="F125" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G125" s="8"/>
+      <c r="H125" s="14"/>
+      <c r="I125" s="8"/>
+      <c r="J125" s="8"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="8">
         <v>20</v>
       </c>
@@ -2767,8 +3307,12 @@
       <c r="F126" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G126" s="8"/>
+      <c r="H126" s="14"/>
+      <c r="I126" s="8"/>
+      <c r="J126" s="8"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <v>20</v>
       </c>
@@ -2785,8 +3329,12 @@
       <c r="F127" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G127" s="8"/>
+      <c r="H127" s="14"/>
+      <c r="I127" s="8"/>
+      <c r="J127" s="8"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
         <v>21</v>
       </c>
@@ -2803,8 +3351,12 @@
       <c r="F128" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G128" s="8"/>
+      <c r="H128" s="14"/>
+      <c r="I128" s="8"/>
+      <c r="J128" s="8"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
         <v>21</v>
       </c>
@@ -2821,8 +3373,12 @@
       <c r="F129" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G129" s="8"/>
+      <c r="H129" s="14"/>
+      <c r="I129" s="8"/>
+      <c r="J129" s="8"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="8">
         <v>21</v>
       </c>
@@ -2839,8 +3395,12 @@
       <c r="F130" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G130" s="8"/>
+      <c r="H130" s="14"/>
+      <c r="I130" s="8"/>
+      <c r="J130" s="8"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
         <v>21</v>
       </c>
@@ -2857,8 +3417,12 @@
       <c r="F131" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G131" s="8"/>
+      <c r="H131" s="14"/>
+      <c r="I131" s="8"/>
+      <c r="J131" s="8"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
         <v>21</v>
       </c>
@@ -2875,8 +3439,12 @@
       <c r="F132" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G132" s="8"/>
+      <c r="H132" s="14"/>
+      <c r="I132" s="8"/>
+      <c r="J132" s="8"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
         <v>21</v>
       </c>
@@ -2893,8 +3461,12 @@
       <c r="F133" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G133" s="8"/>
+      <c r="H133" s="14"/>
+      <c r="I133" s="8"/>
+      <c r="J133" s="8"/>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
         <v>22</v>
       </c>
@@ -2911,8 +3483,12 @@
       <c r="F134" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G134" s="8"/>
+      <c r="H134" s="14"/>
+      <c r="I134" s="8"/>
+      <c r="J134" s="8"/>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
         <v>22</v>
       </c>
@@ -2929,8 +3505,12 @@
       <c r="F135" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G135" s="8"/>
+      <c r="H135" s="14"/>
+      <c r="I135" s="8"/>
+      <c r="J135" s="8"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
         <v>22</v>
       </c>
@@ -2947,8 +3527,12 @@
       <c r="F136" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G136" s="8"/>
+      <c r="H136" s="14"/>
+      <c r="I136" s="8"/>
+      <c r="J136" s="8"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
         <v>22</v>
       </c>
@@ -2965,8 +3549,12 @@
       <c r="F137" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G137" s="8"/>
+      <c r="H137" s="14"/>
+      <c r="I137" s="8"/>
+      <c r="J137" s="8"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
         <v>22</v>
       </c>
@@ -2983,8 +3571,12 @@
       <c r="F138" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G138" s="8"/>
+      <c r="H138" s="14"/>
+      <c r="I138" s="8"/>
+      <c r="J138" s="8"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
         <v>22</v>
       </c>
@@ -3001,8 +3593,12 @@
       <c r="F139" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G139" s="8"/>
+      <c r="H139" s="14"/>
+      <c r="I139" s="8"/>
+      <c r="J139" s="8"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
         <v>23</v>
       </c>
@@ -3019,8 +3615,12 @@
       <c r="F140" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G140" s="8"/>
+      <c r="H140" s="14"/>
+      <c r="I140" s="8"/>
+      <c r="J140" s="8"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <v>23</v>
       </c>
@@ -3037,8 +3637,12 @@
       <c r="F141" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G141" s="8"/>
+      <c r="H141" s="14"/>
+      <c r="I141" s="8"/>
+      <c r="J141" s="8"/>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
         <v>23</v>
       </c>
@@ -3055,8 +3659,12 @@
       <c r="F142" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G142" s="8"/>
+      <c r="H142" s="14"/>
+      <c r="I142" s="8"/>
+      <c r="J142" s="8"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <v>23</v>
       </c>
@@ -3075,8 +3683,12 @@
       <c r="F143" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G143" s="8"/>
+      <c r="H143" s="14"/>
+      <c r="I143" s="8"/>
+      <c r="J143" s="8"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
         <v>23</v>
       </c>
@@ -3093,8 +3705,12 @@
       <c r="F144" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G144" s="8"/>
+      <c r="H144" s="14"/>
+      <c r="I144" s="8"/>
+      <c r="J144" s="8"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
         <v>23</v>
       </c>
@@ -3111,8 +3727,12 @@
       <c r="F145" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G145" s="8"/>
+      <c r="H145" s="14"/>
+      <c r="I145" s="8"/>
+      <c r="J145" s="8"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
         <v>24</v>
       </c>
@@ -3131,8 +3751,12 @@
       <c r="F146" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G146" s="8"/>
+      <c r="H146" s="14"/>
+      <c r="I146" s="8"/>
+      <c r="J146" s="8"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
         <v>24</v>
       </c>
@@ -3149,8 +3773,12 @@
       <c r="F147" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G147" s="8"/>
+      <c r="H147" s="14"/>
+      <c r="I147" s="8"/>
+      <c r="J147" s="8"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
         <v>24</v>
       </c>
@@ -3167,8 +3795,12 @@
       <c r="F148" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G148" s="8"/>
+      <c r="H148" s="14"/>
+      <c r="I148" s="8"/>
+      <c r="J148" s="8"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
         <v>24</v>
       </c>
@@ -3185,8 +3817,12 @@
       <c r="F149" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G149" s="8"/>
+      <c r="H149" s="14"/>
+      <c r="I149" s="8"/>
+      <c r="J149" s="8"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
         <v>24</v>
       </c>
@@ -3203,8 +3839,12 @@
       <c r="F150" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G150" s="8"/>
+      <c r="H150" s="14"/>
+      <c r="I150" s="8"/>
+      <c r="J150" s="8"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
         <v>24</v>
       </c>
@@ -3221,8 +3861,12 @@
       <c r="F151" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G151" s="8"/>
+      <c r="H151" s="14"/>
+      <c r="I151" s="8"/>
+      <c r="J151" s="8"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
         <v>24</v>
       </c>
@@ -3239,8 +3883,12 @@
       <c r="F152" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G152" s="8"/>
+      <c r="H152" s="14"/>
+      <c r="I152" s="8"/>
+      <c r="J152" s="8"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
         <v>25</v>
       </c>
@@ -3257,8 +3905,12 @@
       <c r="F153" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G153" s="8"/>
+      <c r="H153" s="14"/>
+      <c r="I153" s="8"/>
+      <c r="J153" s="8"/>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
         <v>25</v>
       </c>
@@ -3275,8 +3927,12 @@
       <c r="F154" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G154" s="8"/>
+      <c r="H154" s="14"/>
+      <c r="I154" s="8"/>
+      <c r="J154" s="8"/>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
         <v>25</v>
       </c>
@@ -3293,8 +3949,12 @@
       <c r="F155" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G155" s="8"/>
+      <c r="H155" s="14"/>
+      <c r="I155" s="8"/>
+      <c r="J155" s="8"/>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
         <v>25</v>
       </c>
@@ -3311,8 +3971,12 @@
       <c r="F156" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G156" s="8"/>
+      <c r="H156" s="14"/>
+      <c r="I156" s="8"/>
+      <c r="J156" s="8"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
         <v>25</v>
       </c>
@@ -3329,8 +3993,12 @@
       <c r="F157" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G157" s="8"/>
+      <c r="H157" s="14"/>
+      <c r="I157" s="8"/>
+      <c r="J157" s="8"/>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
         <v>25</v>
       </c>
@@ -3347,8 +4015,12 @@
       <c r="F158" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G158" s="8"/>
+      <c r="H158" s="14"/>
+      <c r="I158" s="8"/>
+      <c r="J158" s="8"/>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
         <v>26</v>
       </c>
@@ -3365,8 +4037,12 @@
       <c r="F159" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G159" s="8"/>
+      <c r="H159" s="14"/>
+      <c r="I159" s="8"/>
+      <c r="J159" s="8"/>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
         <v>26</v>
       </c>
@@ -3383,8 +4059,12 @@
       <c r="F160" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G160" s="8"/>
+      <c r="H160" s="14"/>
+      <c r="I160" s="8"/>
+      <c r="J160" s="8"/>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
         <v>26</v>
       </c>
@@ -3401,8 +4081,12 @@
       <c r="F161" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G161" s="8"/>
+      <c r="H161" s="14"/>
+      <c r="I161" s="8"/>
+      <c r="J161" s="8"/>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
         <v>26</v>
       </c>
@@ -3419,8 +4103,12 @@
       <c r="F162" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G162" s="8"/>
+      <c r="H162" s="14"/>
+      <c r="I162" s="8"/>
+      <c r="J162" s="8"/>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
         <v>26</v>
       </c>
@@ -3437,8 +4125,12 @@
       <c r="F163" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G163" s="8"/>
+      <c r="H163" s="14"/>
+      <c r="I163" s="8"/>
+      <c r="J163" s="8"/>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
         <v>26</v>
       </c>
@@ -3455,8 +4147,12 @@
       <c r="F164" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G164" s="8"/>
+      <c r="H164" s="14"/>
+      <c r="I164" s="8"/>
+      <c r="J164" s="8"/>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
         <v>27</v>
       </c>
@@ -3475,8 +4171,12 @@
       <c r="F165" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G165" s="8"/>
+      <c r="H165" s="14"/>
+      <c r="I165" s="8"/>
+      <c r="J165" s="8"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
         <v>27</v>
       </c>
@@ -3493,8 +4193,12 @@
       <c r="F166" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G166" s="8"/>
+      <c r="H166" s="14"/>
+      <c r="I166" s="8"/>
+      <c r="J166" s="8"/>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
         <v>27</v>
       </c>
@@ -3511,8 +4215,12 @@
       <c r="F167" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G167" s="8"/>
+      <c r="H167" s="14"/>
+      <c r="I167" s="8"/>
+      <c r="J167" s="8"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
         <v>27</v>
       </c>
@@ -3529,8 +4237,12 @@
       <c r="F168" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G168" s="8"/>
+      <c r="H168" s="14"/>
+      <c r="I168" s="8"/>
+      <c r="J168" s="8"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
         <v>27</v>
       </c>
@@ -3547,8 +4259,12 @@
       <c r="F169" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G169" s="8"/>
+      <c r="H169" s="14"/>
+      <c r="I169" s="8"/>
+      <c r="J169" s="8"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="8">
         <v>27</v>
       </c>
@@ -3565,8 +4281,12 @@
       <c r="F170" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G170" s="8"/>
+      <c r="H170" s="14"/>
+      <c r="I170" s="8"/>
+      <c r="J170" s="8"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="8">
         <v>27</v>
       </c>
@@ -3583,6 +4303,10 @@
       <c r="F171" s="11">
         <v>1</v>
       </c>
+      <c r="G171" s="8"/>
+      <c r="H171" s="14"/>
+      <c r="I171" s="8"/>
+      <c r="J171" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
